--- a/Files/Prabhat Panel Chart.xlsx
+++ b/Files/Prabhat Panel Chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$466</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$468</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2438,6 +2438,12 @@
   </x:si>
   <x:si>
     <x:t>31/08/2026 to 05/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/09/2026 to 12/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026 to 19/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -2893,7 +2899,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V466"/>
+  <x:dimension ref="A1:V468"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -34534,49 +34540,49 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="E466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="H466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="I466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="J466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="K466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="L466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="M466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="N466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="O466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="P466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="Q466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="R466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="S466" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="T466" s="3" t="s">
         <x:v>41</x:v>
@@ -34588,8 +34594,144 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="467" spans="1:22">
+      <x:c r="A467" s="3" t="s">
+        <x:v>807</x:v>
+      </x:c>
+      <x:c r="B467" s="3" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="C467" s="3" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D467" s="3" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="E467" s="3" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F467" s="3" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G467" s="3" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="H467" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I467" s="3" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="J467" s="3" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="K467" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L467" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="M467" s="3" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="N467" s="3" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="O467" s="3" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="P467" s="3" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="Q467" s="3" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="R467" s="3" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="S467" s="3" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="T467" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U467" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V467" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" spans="1:22">
+      <x:c r="A468" s="3" t="s">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="B468" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C468" s="3" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D468" s="3" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="E468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V468" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V466"/>
+  <x:autoFilter ref="A1:V468"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -34612,39 +34754,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>807</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>808</x:v>
+        <x:v>810</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>809</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>810</x:v>
+        <x:v>812</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>811</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>812</x:v>
+        <x:v>814</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>813</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>465</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>814</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -34652,10 +34794,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>815</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>806</x:v>
+        <x:v>808</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Files/Prabhat Panel Chart.xlsx
+++ b/Files/Prabhat Panel Chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$468</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$469</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2444,6 +2444,9 @@
   </x:si>
   <x:si>
     <x:t>14/09/2026 to 19/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026 to 26/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -2899,7 +2902,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V468"/>
+  <x:dimension ref="A1:V469"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -34676,49 +34679,49 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="E468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="F468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="I468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="J468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="L468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="N468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="O468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="P468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="Q468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="R468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="S468" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="T468" s="3" t="s">
         <x:v>41</x:v>
@@ -34730,8 +34733,76 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="469" spans="1:22">
+      <x:c r="A469" s="3" t="s">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="B469" s="3" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="C469" s="3" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D469" s="3" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E469" s="3" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F469" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G469" s="3" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H469" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I469" s="3" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="J469" s="3" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="K469" s="3" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="L469" s="3" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="M469" s="3" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="N469" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O469" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P469" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q469" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R469" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S469" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T469" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U469" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V469" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V468"/>
+  <x:autoFilter ref="A1:V469"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -34754,39 +34825,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>809</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>810</x:v>
+        <x:v>811</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>811</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>812</x:v>
+        <x:v>813</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>813</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>814</x:v>
+        <x:v>815</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>815</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>467</x:v>
+        <x:v>468</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>816</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -34794,10 +34865,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>817</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>808</x:v>
+        <x:v>809</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
